--- a/민원데이터.xlsx
+++ b/민원데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034FDF4D-FCD6-4624-955E-E4552E7D371B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCCAB9E5-D439-423A-8B8A-89E98DD1891E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1755" yWindow="645" windowWidth="27045" windowHeight="14835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5190" yWindow="435" windowWidth="19005" windowHeight="14835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="208">
   <si>
     <t>민원번호</t>
   </si>
@@ -391,9 +391,6 @@
     <t>2026-03-23</t>
   </si>
   <si>
-    <t>울산 중구 남외동 693-4</t>
-  </si>
-  <si>
     <t>동천 파크골프장 잔디 보식 기간 중 성안 함월구장에서 그라운드골프 이용자와 산책 이용자 다툼 발생</t>
   </si>
   <si>
@@ -642,6 +639,18 @@
   </si>
   <si>
     <t>민원인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성안동 923</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장기과제</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -991,6 +1000,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H76"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="35.875" customWidth="1"/>
+    <col min="4" max="4" width="38.875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1006,7 +1019,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -1318,7 +1331,7 @@
         <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F13" t="s">
         <v>11</v>
@@ -2092,22 +2105,16 @@
         <v>121</v>
       </c>
       <c r="C43" t="s">
+        <v>205</v>
+      </c>
+      <c r="D43" t="s">
         <v>122</v>
       </c>
-      <c r="D43" t="s">
-        <v>123</v>
-      </c>
       <c r="E43" t="s">
         <v>10</v>
       </c>
       <c r="F43" t="s">
         <v>11</v>
-      </c>
-      <c r="G43">
-        <v>35.563590041701602</v>
-      </c>
-      <c r="H43">
-        <v>129.352649054072</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
@@ -2118,10 +2125,10 @@
         <v>121</v>
       </c>
       <c r="C44" t="s">
+        <v>123</v>
+      </c>
+      <c r="D44" t="s">
         <v>124</v>
-      </c>
-      <c r="D44" t="s">
-        <v>125</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
@@ -2141,13 +2148,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C45" t="s">
         <v>112</v>
       </c>
       <c r="D45" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E45" t="s">
         <v>64</v>
@@ -2167,19 +2174,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
+        <v>127</v>
+      </c>
+      <c r="D46" t="s">
         <v>128</v>
       </c>
-      <c r="D46" t="s">
-        <v>129</v>
-      </c>
       <c r="E46" t="s">
         <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>60</v>
+        <v>206</v>
       </c>
       <c r="G46">
         <v>35.557219330149202</v>
@@ -2193,13 +2200,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>129</v>
+      </c>
+      <c r="C47" t="s">
         <v>130</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>131</v>
-      </c>
-      <c r="D47" t="s">
-        <v>132</v>
       </c>
       <c r="E47" t="s">
         <v>10</v>
@@ -2219,16 +2226,16 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
+        <v>132</v>
+      </c>
+      <c r="C48" t="s">
         <v>133</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>134</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>135</v>
-      </c>
-      <c r="E48" t="s">
-        <v>136</v>
       </c>
       <c r="F48" t="s">
         <v>11</v>
@@ -2245,13 +2252,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>136</v>
+      </c>
+      <c r="C49" t="s">
         <v>137</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>138</v>
-      </c>
-      <c r="D49" t="s">
-        <v>139</v>
       </c>
       <c r="E49" t="s">
         <v>10</v>
@@ -2271,13 +2278,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C50" t="s">
+        <v>139</v>
+      </c>
+      <c r="D50" t="s">
         <v>140</v>
-      </c>
-      <c r="D50" t="s">
-        <v>141</v>
       </c>
       <c r="E50" t="s">
         <v>93</v>
@@ -2297,19 +2304,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>141</v>
+      </c>
+      <c r="C51" t="s">
         <v>142</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>143</v>
       </c>
-      <c r="D51" t="s">
-        <v>144</v>
-      </c>
       <c r="E51" t="s">
         <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>60</v>
+        <v>206</v>
       </c>
       <c r="G51">
         <v>35.562228786253897</v>
@@ -2323,13 +2330,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>141</v>
+      </c>
+      <c r="C52" t="s">
         <v>142</v>
       </c>
-      <c r="C52" t="s">
-        <v>143</v>
-      </c>
       <c r="D52" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
@@ -2349,13 +2356,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C53" t="s">
+        <v>145</v>
+      </c>
+      <c r="D53" t="s">
         <v>146</v>
-      </c>
-      <c r="D53" t="s">
-        <v>147</v>
       </c>
       <c r="E53" t="s">
         <v>10</v>
@@ -2375,13 +2382,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C54" t="s">
         <v>109</v>
       </c>
       <c r="D54" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E54" t="s">
         <v>10</v>
@@ -2401,19 +2408,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C55" t="s">
+        <v>149</v>
+      </c>
+      <c r="D55" t="s">
         <v>150</v>
       </c>
-      <c r="D55" t="s">
-        <v>151</v>
-      </c>
       <c r="E55" t="s">
         <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>60</v>
+        <v>207</v>
       </c>
       <c r="G55">
         <v>35.558800966055898</v>
@@ -2427,13 +2434,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>151</v>
+      </c>
+      <c r="C56" t="s">
         <v>152</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>153</v>
-      </c>
-      <c r="D56" t="s">
-        <v>154</v>
       </c>
       <c r="E56" t="s">
         <v>36</v>
@@ -2453,13 +2460,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
+        <v>154</v>
+      </c>
+      <c r="C57" t="s">
         <v>155</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>156</v>
-      </c>
-      <c r="D57" t="s">
-        <v>157</v>
       </c>
       <c r="E57" t="s">
         <v>36</v>
@@ -2479,13 +2486,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>157</v>
+      </c>
+      <c r="C58" t="s">
         <v>158</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>159</v>
-      </c>
-      <c r="D58" t="s">
-        <v>160</v>
       </c>
       <c r="E58" t="s">
         <v>64</v>
@@ -2505,13 +2512,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>160</v>
+      </c>
+      <c r="C59" t="s">
         <v>161</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>162</v>
-      </c>
-      <c r="D59" t="s">
-        <v>163</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -2531,13 +2538,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
+        <v>163</v>
+      </c>
+      <c r="C60" t="s">
         <v>164</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>165</v>
-      </c>
-      <c r="D60" t="s">
-        <v>166</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
@@ -2557,13 +2564,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C61" t="s">
+        <v>166</v>
+      </c>
+      <c r="D61" t="s">
         <v>167</v>
-      </c>
-      <c r="D61" t="s">
-        <v>168</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
@@ -2583,13 +2590,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C62" t="s">
+        <v>168</v>
+      </c>
+      <c r="D62" t="s">
         <v>169</v>
-      </c>
-      <c r="D62" t="s">
-        <v>170</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
@@ -2609,13 +2616,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C63" t="s">
+        <v>170</v>
+      </c>
+      <c r="D63" t="s">
         <v>171</v>
-      </c>
-      <c r="D63" t="s">
-        <v>172</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
@@ -2635,13 +2642,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
+        <v>172</v>
+      </c>
+      <c r="C64" t="s">
         <v>173</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>174</v>
-      </c>
-      <c r="D64" t="s">
-        <v>175</v>
       </c>
       <c r="E64" t="s">
         <v>36</v>
@@ -2661,13 +2668,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C65" t="s">
+        <v>175</v>
+      </c>
+      <c r="D65" t="s">
         <v>176</v>
-      </c>
-      <c r="D65" t="s">
-        <v>177</v>
       </c>
       <c r="E65" t="s">
         <v>36</v>
@@ -2687,13 +2694,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>177</v>
+      </c>
+      <c r="C66" t="s">
         <v>178</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>179</v>
-      </c>
-      <c r="D66" t="s">
-        <v>180</v>
       </c>
       <c r="E66" t="s">
         <v>10</v>
@@ -2713,13 +2720,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C67" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D67" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E67" t="s">
         <v>10</v>
@@ -2739,13 +2746,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C68" t="s">
+        <v>181</v>
+      </c>
+      <c r="D68" t="s">
         <v>182</v>
-      </c>
-      <c r="D68" t="s">
-        <v>183</v>
       </c>
       <c r="E68" t="s">
         <v>10</v>
@@ -2765,13 +2772,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>183</v>
+      </c>
+      <c r="C69" t="s">
         <v>184</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>185</v>
-      </c>
-      <c r="D69" t="s">
-        <v>186</v>
       </c>
       <c r="E69" t="s">
         <v>82</v>
@@ -2791,13 +2798,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>186</v>
+      </c>
+      <c r="C70" t="s">
+        <v>166</v>
+      </c>
+      <c r="D70" t="s">
         <v>187</v>
-      </c>
-      <c r="C70" t="s">
-        <v>167</v>
-      </c>
-      <c r="D70" t="s">
-        <v>188</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
@@ -2817,19 +2824,19 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>188</v>
+      </c>
+      <c r="C71" t="s">
         <v>189</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
         <v>190</v>
-      </c>
-      <c r="D71" t="s">
-        <v>191</v>
       </c>
       <c r="E71" t="s">
         <v>82</v>
       </c>
       <c r="F71" t="s">
-        <v>60</v>
+        <v>206</v>
       </c>
       <c r="G71">
         <v>35.5609444477629</v>
@@ -2843,13 +2850,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>191</v>
+      </c>
+      <c r="C72" t="s">
         <v>192</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>193</v>
-      </c>
-      <c r="D72" t="s">
-        <v>194</v>
       </c>
       <c r="E72" t="s">
         <v>10</v>
@@ -2869,13 +2876,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C73" t="s">
+        <v>194</v>
+      </c>
+      <c r="D73" t="s">
         <v>195</v>
-      </c>
-      <c r="D73" t="s">
-        <v>196</v>
       </c>
       <c r="E73" t="s">
         <v>10</v>
@@ -2895,13 +2902,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C74" t="s">
+        <v>196</v>
+      </c>
+      <c r="D74" t="s">
         <v>197</v>
-      </c>
-      <c r="D74" t="s">
-        <v>198</v>
       </c>
       <c r="E74" t="s">
         <v>10</v>
@@ -2921,13 +2928,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C75" t="s">
+        <v>198</v>
+      </c>
+      <c r="D75" t="s">
         <v>199</v>
-      </c>
-      <c r="D75" t="s">
-        <v>200</v>
       </c>
       <c r="E75" t="s">
         <v>93</v>
@@ -2947,19 +2954,19 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
+        <v>200</v>
+      </c>
+      <c r="C76" t="s">
         <v>201</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>202</v>
       </c>
-      <c r="D76" t="s">
-        <v>203</v>
-      </c>
       <c r="E76" t="s">
         <v>10</v>
       </c>
       <c r="F76" t="s">
-        <v>60</v>
+        <v>206</v>
       </c>
       <c r="G76">
         <v>35.565261990764498</v>

--- a/민원데이터.xlsx
+++ b/민원데이터.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\민원관리 대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCCAB9E5-D439-423A-8B8A-89E98DD1891E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8248AB9C-4664-4886-B8E6-F786F8B1F289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5190" yWindow="435" windowWidth="19005" windowHeight="14835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="285" yWindow="405" windowWidth="22935" windowHeight="14835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="223">
   <si>
     <t>민원번호</t>
   </si>
@@ -651,6 +651,65 @@
   </si>
   <si>
     <t>장기과제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학성동 옥성공원 수목 정비 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>학성동 옥성공원 내 정자~학성탕 구간 방역 필요</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025년도 내황초 후문 산책로/자전거길 혼재로 안전위험 가중 지적. 자전거길 정비사업 경과 문의</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>반구동 582-2 학성종합상가 내 우수관/하수관 혼재로 위생관리 사각 발생</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>학성1길 63-6 방역 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>김태욱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이명녀</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>완료</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복산동 손골2길5 동덕현대아파트 104동 파손 탄력봉에 걸려 넘어지는 사례 발생하여 제거 요청</t>
+  </si>
+  <si>
+    <t>울산 중구 복산동 319</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 학성동 371-15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 582-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 845</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 학성동 156-4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -658,7 +717,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -670,6 +729,20 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -694,8 +767,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -998,14 +1087,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H76"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H82"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.875" customWidth="1"/>
     <col min="4" max="4" width="38.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1031,7 +1121,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1057,7 +1147,7 @@
         <v>129.334708123821</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1083,7 +1173,7 @@
         <v>129.34914011636599</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1109,7 +1199,7 @@
         <v>129.341655674116</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1135,7 +1225,7 @@
         <v>129.348784402462</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1161,7 +1251,7 @@
         <v>129.328386461436</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1187,7 +1277,7 @@
         <v>129.293406307109</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1213,7 +1303,7 @@
         <v>129.321138541696</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1239,7 +1329,7 @@
         <v>129.336443953188</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1265,7 +1355,7 @@
         <v>129.35126645610401</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1291,7 +1381,7 @@
         <v>129.34604022411801</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1317,7 +1407,7 @@
         <v>129.34512228457299</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1343,7 +1433,7 @@
         <v>129.265769674285</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1369,7 +1459,7 @@
         <v>129.328832230009</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1395,7 +1485,7 @@
         <v>129.32766567982</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1421,7 +1511,7 @@
         <v>129.32605295352801</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1447,7 +1537,7 @@
         <v>129.32736074607899</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1473,7 +1563,7 @@
         <v>129.327571456708</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1499,7 +1589,7 @@
         <v>129.26688519197299</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1525,7 +1615,7 @@
         <v>129.29811305216501</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1551,7 +1641,7 @@
         <v>129.29811305216501</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1577,7 +1667,7 @@
         <v>129.300962239363</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1603,7 +1693,7 @@
         <v>129.30058825465301</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1629,7 +1719,7 @@
         <v>129.30058825465301</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1655,7 +1745,7 @@
         <v>129.32200364813099</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1681,7 +1771,7 @@
         <v>129.32531570361701</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1707,7 +1797,7 @@
         <v>129.31827211577701</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1733,7 +1823,7 @@
         <v>129.3211136704</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1759,7 +1849,7 @@
         <v>129.28046149747701</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1785,7 +1875,7 @@
         <v>129.34220700976999</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1811,7 +1901,7 @@
         <v>129.308375901956</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1837,7 +1927,7 @@
         <v>129.279177893774</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1863,7 +1953,7 @@
         <v>129.31901602761101</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1889,7 +1979,7 @@
         <v>129.346181351555</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1915,7 +2005,7 @@
         <v>129.32388107690801</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1941,7 +2031,7 @@
         <v>129.33754632059299</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1967,7 +2057,7 @@
         <v>129.33754632059299</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1993,7 +2083,7 @@
         <v>129.32938991855301</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2019,7 +2109,7 @@
         <v>129.30858345615701</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2045,7 +2135,7 @@
         <v>129.32189922619699</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2071,7 +2161,7 @@
         <v>129.32189922619699</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2097,7 +2187,7 @@
         <v>129.31846356317999</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2117,7 +2207,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2143,7 +2233,7 @@
         <v>129.31021759453901</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2169,7 +2259,7 @@
         <v>129.30858345615701</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2195,7 +2285,7 @@
         <v>129.334901038727</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2221,7 +2311,7 @@
         <v>129.32268218764199</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2247,7 +2337,7 @@
         <v>129.32704582909801</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2273,7 +2363,7 @@
         <v>129.32991157348201</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2299,7 +2389,7 @@
         <v>129.30194271522601</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2325,7 +2415,7 @@
         <v>129.31749376133601</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2351,7 +2441,7 @@
         <v>129.31749376133601</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2377,7 +2467,7 @@
         <v>129.337495790666</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2403,7 +2493,7 @@
         <v>129.32938991855301</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2429,7 +2519,7 @@
         <v>129.33276957269501</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2455,7 +2545,7 @@
         <v>129.34719219842799</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2481,7 +2571,7 @@
         <v>129.337436690766</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2507,7 +2597,7 @@
         <v>129.30959998798701</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2533,7 +2623,7 @@
         <v>129.34773887451399</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2559,7 +2649,7 @@
         <v>129.32796607151101</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2585,7 +2675,7 @@
         <v>129.32761912511799</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2611,7 +2701,7 @@
         <v>129.33454593378599</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2637,7 +2727,7 @@
         <v>129.33141894784401</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2663,7 +2753,7 @@
         <v>129.33133707067299</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2689,7 +2779,7 @@
         <v>129.34715485530299</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2715,7 +2805,7 @@
         <v>129.33926986466699</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2741,7 +2831,7 @@
         <v>129.32761912511799</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2767,7 +2857,7 @@
         <v>129.309630937603</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2793,7 +2883,7 @@
         <v>129.31561270768299</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2819,7 +2909,7 @@
         <v>129.32761912511799</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2845,7 +2935,7 @@
         <v>129.331943041014</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2871,7 +2961,7 @@
         <v>129.327504233165</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2897,7 +2987,7 @@
         <v>129.33393651216301</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2923,57 +3013,189 @@
         <v>129.32832432580301</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75">
+    <row r="75" spans="1:8">
+      <c r="A75" s="1">
         <v>74</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E75" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F75" t="s">
-        <v>11</v>
-      </c>
-      <c r="G75">
+      <c r="F75" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G75" s="1">
         <v>35.578724191624801</v>
       </c>
-      <c r="H75">
+      <c r="H75" s="1">
         <v>129.26523649600099</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76">
+    <row r="76" spans="1:8">
+      <c r="A76" s="1">
         <v>75</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E76" t="s">
-        <v>10</v>
-      </c>
-      <c r="F76" t="s">
+      <c r="E76" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="G76">
+      <c r="G76" s="1">
         <v>35.565261990764498</v>
       </c>
-      <c r="H76">
+      <c r="H76" s="1">
         <v>129.32976548908499</v>
       </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2">
+        <v>46160</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2">
+        <v>46160</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2">
+        <v>46164</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2">
+        <v>46164</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2">
+        <v>46168</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2">
+        <v>46168</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/민원데이터.xlsx
+++ b/민원데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\민원관리 대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8248AB9C-4664-4886-B8E6-F786F8B1F289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FBDC633-8AA4-49C7-B48D-26285898E3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="285" yWindow="405" windowWidth="22935" windowHeight="14835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="1365" windowWidth="22725" windowHeight="14835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -767,22 +767,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2978,7 +2974,7 @@
         <v>10</v>
       </c>
       <c r="F73" t="s">
-        <v>60</v>
+        <v>206</v>
       </c>
       <c r="G73">
         <v>35.555089355611798</v>
@@ -3004,7 +3000,7 @@
         <v>10</v>
       </c>
       <c r="F74" t="s">
-        <v>60</v>
+        <v>206</v>
       </c>
       <c r="G74">
         <v>35.556408038012002</v>
@@ -3014,188 +3010,176 @@
       </c>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="1">
+      <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" t="s">
         <v>191</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" t="s">
         <v>198</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="D75" t="s">
         <v>199</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E75" t="s">
         <v>93</v>
       </c>
-      <c r="F75" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G75" s="1">
+      <c r="F75" t="s">
+        <v>11</v>
+      </c>
+      <c r="G75">
         <v>35.578724191624801</v>
       </c>
-      <c r="H75" s="1">
+      <c r="H75">
         <v>129.26523649600099</v>
       </c>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="1">
+      <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" t="s">
         <v>200</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" t="s">
         <v>201</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D76" t="s">
         <v>202</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F76" s="1" t="s">
+      <c r="E76" t="s">
+        <v>10</v>
+      </c>
+      <c r="F76" t="s">
         <v>206</v>
       </c>
-      <c r="G76" s="1">
+      <c r="G76">
         <v>35.565261990764498</v>
       </c>
-      <c r="H76" s="1">
+      <c r="H76">
         <v>129.32976548908499</v>
       </c>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="1">
+      <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" s="2">
+      <c r="B77" s="1">
         <v>46160</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" t="s">
         <v>222</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D77" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="E77" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="F77" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="1">
+      <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78" s="1">
         <v>46160</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" t="s">
         <v>222</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E78" s="3" t="s">
+      <c r="E78" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F78" s="3" t="s">
+      <c r="F78" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="1">
+      <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" s="2">
+      <c r="B79" s="1">
         <v>46164</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" t="s">
         <v>221</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="E79" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="F79" s="3" t="s">
+      <c r="F79" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="1">
+      <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" s="2">
+      <c r="B80" s="1">
         <v>46164</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" t="s">
         <v>220</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E80" s="3" t="s">
+      <c r="E80" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="F80" s="4" t="s">
+      <c r="F80" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-    </row>
-    <row r="81" spans="1:8">
-      <c r="A81" s="1">
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81" s="2">
+      <c r="B81" s="1">
         <v>46168</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" t="s">
         <v>219</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D81" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="E81" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="F81" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-    </row>
-    <row r="82" spans="1:8">
-      <c r="A82" s="1">
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82">
         <v>81</v>
       </c>
-      <c r="B82" s="2">
+      <c r="B82" s="1">
         <v>46168</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" t="s">
         <v>218</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D82" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="E82" s="5" t="s">
+      <c r="E82" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F82" s="6" t="s">
+      <c r="F82" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/민원데이터.xlsx
+++ b/민원데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\민원관리 대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FBDC633-8AA4-49C7-B48D-26285898E3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A837950-F832-4E97-A3A7-9127616CA408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1365" windowWidth="22725" windowHeight="14835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="1365" windowWidth="22725" windowHeight="14835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -511,9 +511,6 @@
     <t>울산 중구 반구동 693-3</t>
   </si>
   <si>
-    <t>반사경 설치 요청(김정희 회장, 길이 좋고 경사로로 사고위험 높음)</t>
-  </si>
-  <si>
     <t>2026-04-21</t>
   </si>
   <si>
@@ -710,6 +707,10 @@
   </si>
   <si>
     <t>울산 중구 학성동 156-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>반사경 설치 요청(김정희 회장, 길이 좁고 경사로로 사고위험 높음)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -717,7 +718,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1084,14 +1085,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H82"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.875" customWidth="1"/>
     <col min="4" max="4" width="38.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1105,7 +1106,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -1117,7 +1118,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1143,7 +1144,7 @@
         <v>129.334708123821</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1169,7 +1170,7 @@
         <v>129.34914011636599</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1195,7 +1196,7 @@
         <v>129.341655674116</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1221,7 +1222,7 @@
         <v>129.348784402462</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1247,7 +1248,7 @@
         <v>129.328386461436</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1273,7 +1274,7 @@
         <v>129.293406307109</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1299,7 +1300,7 @@
         <v>129.321138541696</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1325,7 +1326,7 @@
         <v>129.336443953188</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1351,7 +1352,7 @@
         <v>129.35126645610401</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1377,7 +1378,7 @@
         <v>129.34604022411801</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1403,7 +1404,7 @@
         <v>129.34512228457299</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1417,7 +1418,7 @@
         <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F13" t="s">
         <v>11</v>
@@ -1429,7 +1430,7 @@
         <v>129.265769674285</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1455,7 +1456,7 @@
         <v>129.328832230009</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1481,7 +1482,7 @@
         <v>129.32766567982</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1507,7 +1508,7 @@
         <v>129.32605295352801</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1533,7 +1534,7 @@
         <v>129.32736074607899</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1559,7 +1560,7 @@
         <v>129.327571456708</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1585,7 +1586,7 @@
         <v>129.26688519197299</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1611,7 +1612,7 @@
         <v>129.29811305216501</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1637,7 +1638,7 @@
         <v>129.29811305216501</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1663,7 +1664,7 @@
         <v>129.300962239363</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1689,7 +1690,7 @@
         <v>129.30058825465301</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1715,7 +1716,7 @@
         <v>129.30058825465301</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1741,7 +1742,7 @@
         <v>129.32200364813099</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1767,7 +1768,7 @@
         <v>129.32531570361701</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1793,7 +1794,7 @@
         <v>129.31827211577701</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1819,7 +1820,7 @@
         <v>129.3211136704</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1845,7 +1846,7 @@
         <v>129.28046149747701</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1871,7 +1872,7 @@
         <v>129.34220700976999</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1897,7 +1898,7 @@
         <v>129.308375901956</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1923,7 +1924,7 @@
         <v>129.279177893774</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1949,7 +1950,7 @@
         <v>129.31901602761101</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1975,7 +1976,7 @@
         <v>129.346181351555</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2001,7 +2002,7 @@
         <v>129.32388107690801</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2027,7 +2028,7 @@
         <v>129.33754632059299</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2053,7 +2054,7 @@
         <v>129.33754632059299</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2079,7 +2080,7 @@
         <v>129.32938991855301</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2105,7 +2106,7 @@
         <v>129.30858345615701</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2131,7 +2132,7 @@
         <v>129.32189922619699</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2157,7 +2158,7 @@
         <v>129.32189922619699</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2183,7 +2184,7 @@
         <v>129.31846356317999</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2191,7 +2192,7 @@
         <v>121</v>
       </c>
       <c r="C43" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D43" t="s">
         <v>122</v>
@@ -2203,7 +2204,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2229,7 +2230,7 @@
         <v>129.31021759453901</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2255,7 +2256,7 @@
         <v>129.30858345615701</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2272,7 +2273,7 @@
         <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G46">
         <v>35.557219330149202</v>
@@ -2281,7 +2282,7 @@
         <v>129.334901038727</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2307,7 +2308,7 @@
         <v>129.32268218764199</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2333,7 +2334,7 @@
         <v>129.32704582909801</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2359,7 +2360,7 @@
         <v>129.32991157348201</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2385,7 +2386,7 @@
         <v>129.30194271522601</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2402,7 +2403,7 @@
         <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G51">
         <v>35.562228786253897</v>
@@ -2411,7 +2412,7 @@
         <v>129.31749376133601</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2437,7 +2438,7 @@
         <v>129.31749376133601</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2463,7 +2464,7 @@
         <v>129.337495790666</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2489,7 +2490,7 @@
         <v>129.32938991855301</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2506,7 +2507,7 @@
         <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G55">
         <v>35.558800966055898</v>
@@ -2515,7 +2516,7 @@
         <v>129.33276957269501</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2541,7 +2542,7 @@
         <v>129.34719219842799</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2567,7 +2568,7 @@
         <v>129.337436690766</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2593,7 +2594,7 @@
         <v>129.30959998798701</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2604,7 +2605,7 @@
         <v>161</v>
       </c>
       <c r="D59" t="s">
-        <v>162</v>
+        <v>222</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -2619,18 +2620,18 @@
         <v>129.34773887451399</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
+        <v>162</v>
+      </c>
+      <c r="C60" t="s">
         <v>163</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>164</v>
-      </c>
-      <c r="D60" t="s">
-        <v>165</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
@@ -2645,18 +2646,18 @@
         <v>129.32796607151101</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C61" t="s">
+        <v>165</v>
+      </c>
+      <c r="D61" t="s">
         <v>166</v>
-      </c>
-      <c r="D61" t="s">
-        <v>167</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
@@ -2671,18 +2672,18 @@
         <v>129.32761912511799</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C62" t="s">
+        <v>167</v>
+      </c>
+      <c r="D62" t="s">
         <v>168</v>
-      </c>
-      <c r="D62" t="s">
-        <v>169</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
@@ -2697,18 +2698,18 @@
         <v>129.33454593378599</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C63" t="s">
+        <v>169</v>
+      </c>
+      <c r="D63" t="s">
         <v>170</v>
-      </c>
-      <c r="D63" t="s">
-        <v>171</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
@@ -2723,18 +2724,18 @@
         <v>129.33141894784401</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
+        <v>171</v>
+      </c>
+      <c r="C64" t="s">
         <v>172</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>173</v>
-      </c>
-      <c r="D64" t="s">
-        <v>174</v>
       </c>
       <c r="E64" t="s">
         <v>36</v>
@@ -2749,18 +2750,18 @@
         <v>129.33133707067299</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C65" t="s">
+        <v>174</v>
+      </c>
+      <c r="D65" t="s">
         <v>175</v>
-      </c>
-      <c r="D65" t="s">
-        <v>176</v>
       </c>
       <c r="E65" t="s">
         <v>36</v>
@@ -2775,18 +2776,18 @@
         <v>129.34715485530299</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>176</v>
+      </c>
+      <c r="C66" t="s">
         <v>177</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>178</v>
-      </c>
-      <c r="D66" t="s">
-        <v>179</v>
       </c>
       <c r="E66" t="s">
         <v>10</v>
@@ -2801,18 +2802,18 @@
         <v>129.33926986466699</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C67" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D67" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E67" t="s">
         <v>10</v>
@@ -2827,18 +2828,18 @@
         <v>129.32761912511799</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C68" t="s">
+        <v>180</v>
+      </c>
+      <c r="D68" t="s">
         <v>181</v>
-      </c>
-      <c r="D68" t="s">
-        <v>182</v>
       </c>
       <c r="E68" t="s">
         <v>10</v>
@@ -2853,18 +2854,18 @@
         <v>129.309630937603</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>182</v>
+      </c>
+      <c r="C69" t="s">
         <v>183</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>184</v>
-      </c>
-      <c r="D69" t="s">
-        <v>185</v>
       </c>
       <c r="E69" t="s">
         <v>82</v>
@@ -2879,18 +2880,18 @@
         <v>129.31561270768299</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>185</v>
+      </c>
+      <c r="C70" t="s">
+        <v>165</v>
+      </c>
+      <c r="D70" t="s">
         <v>186</v>
-      </c>
-      <c r="C70" t="s">
-        <v>166</v>
-      </c>
-      <c r="D70" t="s">
-        <v>187</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
@@ -2905,24 +2906,24 @@
         <v>129.32761912511799</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>187</v>
+      </c>
+      <c r="C71" t="s">
         <v>188</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
         <v>189</v>
-      </c>
-      <c r="D71" t="s">
-        <v>190</v>
       </c>
       <c r="E71" t="s">
         <v>82</v>
       </c>
       <c r="F71" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G71">
         <v>35.5609444477629</v>
@@ -2931,18 +2932,18 @@
         <v>129.331943041014</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>190</v>
+      </c>
+      <c r="C72" t="s">
         <v>191</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>192</v>
-      </c>
-      <c r="D72" t="s">
-        <v>193</v>
       </c>
       <c r="E72" t="s">
         <v>10</v>
@@ -2957,24 +2958,24 @@
         <v>129.327504233165</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C73" t="s">
+        <v>193</v>
+      </c>
+      <c r="D73" t="s">
         <v>194</v>
       </c>
-      <c r="D73" t="s">
-        <v>195</v>
-      </c>
       <c r="E73" t="s">
         <v>10</v>
       </c>
       <c r="F73" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G73">
         <v>35.555089355611798</v>
@@ -2983,24 +2984,24 @@
         <v>129.33393651216301</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C74" t="s">
+        <v>195</v>
+      </c>
+      <c r="D74" t="s">
         <v>196</v>
       </c>
-      <c r="D74" t="s">
-        <v>197</v>
-      </c>
       <c r="E74" t="s">
         <v>10</v>
       </c>
       <c r="F74" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G74">
         <v>35.556408038012002</v>
@@ -3009,18 +3010,18 @@
         <v>129.32832432580301</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C75" t="s">
+        <v>197</v>
+      </c>
+      <c r="D75" t="s">
         <v>198</v>
-      </c>
-      <c r="D75" t="s">
-        <v>199</v>
       </c>
       <c r="E75" t="s">
         <v>93</v>
@@ -3035,24 +3036,24 @@
         <v>129.26523649600099</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
+        <v>199</v>
+      </c>
+      <c r="C76" t="s">
         <v>200</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>201</v>
       </c>
-      <c r="D76" t="s">
-        <v>202</v>
-      </c>
       <c r="E76" t="s">
         <v>10</v>
       </c>
       <c r="F76" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G76">
         <v>35.565261990764498</v>
@@ -3061,7 +3062,7 @@
         <v>129.32976548908499</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -3069,19 +3070,19 @@
         <v>46160</v>
       </c>
       <c r="C77" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -3089,19 +3090,19 @@
         <v>46160</v>
       </c>
       <c r="C78" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -3109,19 +3110,19 @@
         <v>46164</v>
       </c>
       <c r="C79" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E79" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F79" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="F79" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8">
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -3129,19 +3130,19 @@
         <v>46164</v>
       </c>
       <c r="C80" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -3149,19 +3150,19 @@
         <v>46168</v>
       </c>
       <c r="C81" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D81" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E81" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E81" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="F81" s="3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -3169,16 +3170,16 @@
         <v>46168</v>
       </c>
       <c r="C82" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/민원데이터.xlsx
+++ b/민원데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\민원관리 대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A837950-F832-4E97-A3A7-9127616CA408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD72BE1-70F0-40A5-B80B-1897C97CE45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="1365" windowWidth="22725" windowHeight="14835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="1365" windowWidth="22725" windowHeight="14835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -601,19 +601,10 @@
     <t>울산 중구 학산동 80-1</t>
   </si>
   <si>
-    <t>번영로 368, 370 사이 전봇대에서 쓰레기 불법투기 잦아 CCTV 설치 요청</t>
-  </si>
-  <si>
     <t>울산 중구 학성동 464-39</t>
   </si>
   <si>
-    <t>창현하우징 앞 맨홀뚜껑 유격 발생</t>
-  </si>
-  <si>
     <t>울산 중구 학성동 436-11</t>
-  </si>
-  <si>
-    <t>학성동 구역전족발 앞 횡단보도 맨홀뚜껑 유격 발생 및 주변 아스콘 파손으로 주민 불안 가중</t>
   </si>
   <si>
     <t>울산 중구 다운동 247-5</t>
@@ -702,15 +693,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>울산 중구 반구동 845</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>울산 중구 학성동 156-4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>반사경 설치 요청(김정희 회장, 길이 좁고 경사로로 사고위험 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 401-64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학성동 구역전족발 앞 횡단보도 맨홀뚜껑 유격 발생 및 주변 아스콘 파손 정비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>창현하우징 앞 맨홀뚜껑 유격 정비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>번영로 368, 370 사이 전봇대에서 쓰레기 불법투기 잦아 CCTV 설치 요청</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -718,7 +721,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1085,14 +1088,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H82"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.875" customWidth="1"/>
     <col min="4" max="4" width="38.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1106,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -1118,7 +1121,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1144,7 +1147,7 @@
         <v>129.334708123821</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1170,7 +1173,7 @@
         <v>129.34914011636599</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1196,7 +1199,7 @@
         <v>129.341655674116</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1222,7 +1225,7 @@
         <v>129.348784402462</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1248,7 +1251,7 @@
         <v>129.328386461436</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1274,7 +1277,7 @@
         <v>129.293406307109</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1300,7 +1303,7 @@
         <v>129.321138541696</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1326,7 +1329,7 @@
         <v>129.336443953188</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1352,7 +1355,7 @@
         <v>129.35126645610401</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1378,7 +1381,7 @@
         <v>129.34604022411801</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1404,7 +1407,7 @@
         <v>129.34512228457299</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1418,7 +1421,7 @@
         <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F13" t="s">
         <v>11</v>
@@ -1430,7 +1433,7 @@
         <v>129.265769674285</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1456,7 +1459,7 @@
         <v>129.328832230009</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1482,7 +1485,7 @@
         <v>129.32766567982</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1508,7 +1511,7 @@
         <v>129.32605295352801</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1534,7 +1537,7 @@
         <v>129.32736074607899</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1560,7 +1563,7 @@
         <v>129.327571456708</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1586,7 +1589,7 @@
         <v>129.26688519197299</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1612,7 +1615,7 @@
         <v>129.29811305216501</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1638,7 +1641,7 @@
         <v>129.29811305216501</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1664,7 +1667,7 @@
         <v>129.300962239363</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1690,7 +1693,7 @@
         <v>129.30058825465301</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1716,7 +1719,7 @@
         <v>129.30058825465301</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1742,7 +1745,7 @@
         <v>129.32200364813099</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1768,7 +1771,7 @@
         <v>129.32531570361701</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1794,7 +1797,7 @@
         <v>129.31827211577701</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1820,7 +1823,7 @@
         <v>129.3211136704</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1846,7 +1849,7 @@
         <v>129.28046149747701</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1872,7 +1875,7 @@
         <v>129.34220700976999</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1898,7 +1901,7 @@
         <v>129.308375901956</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1924,7 +1927,7 @@
         <v>129.279177893774</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1950,7 +1953,7 @@
         <v>129.31901602761101</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1976,7 +1979,7 @@
         <v>129.346181351555</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2002,7 +2005,7 @@
         <v>129.32388107690801</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2028,7 +2031,7 @@
         <v>129.33754632059299</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2054,7 +2057,7 @@
         <v>129.33754632059299</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2080,7 +2083,7 @@
         <v>129.32938991855301</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2106,7 +2109,7 @@
         <v>129.30858345615701</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2132,7 +2135,7 @@
         <v>129.32189922619699</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2158,7 +2161,7 @@
         <v>129.32189922619699</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2184,7 +2187,7 @@
         <v>129.31846356317999</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2192,7 +2195,7 @@
         <v>121</v>
       </c>
       <c r="C43" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D43" t="s">
         <v>122</v>
@@ -2204,7 +2207,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2230,7 +2233,7 @@
         <v>129.31021759453901</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2256,7 +2259,7 @@
         <v>129.30858345615701</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2273,7 +2276,7 @@
         <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G46">
         <v>35.557219330149202</v>
@@ -2282,7 +2285,7 @@
         <v>129.334901038727</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2308,7 +2311,7 @@
         <v>129.32268218764199</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2334,7 +2337,7 @@
         <v>129.32704582909801</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2360,7 +2363,7 @@
         <v>129.32991157348201</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2386,7 +2389,7 @@
         <v>129.30194271522601</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2403,7 +2406,7 @@
         <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G51">
         <v>35.562228786253897</v>
@@ -2412,7 +2415,7 @@
         <v>129.31749376133601</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2438,7 +2441,7 @@
         <v>129.31749376133601</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2464,7 +2467,7 @@
         <v>129.337495790666</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2490,7 +2493,7 @@
         <v>129.32938991855301</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2507,7 +2510,7 @@
         <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G55">
         <v>35.558800966055898</v>
@@ -2516,7 +2519,7 @@
         <v>129.33276957269501</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2542,7 +2545,7 @@
         <v>129.34719219842799</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2568,7 +2571,7 @@
         <v>129.337436690766</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2594,7 +2597,7 @@
         <v>129.30959998798701</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2605,7 +2608,7 @@
         <v>161</v>
       </c>
       <c r="D59" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -2620,7 +2623,7 @@
         <v>129.34773887451399</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2646,7 +2649,7 @@
         <v>129.32796607151101</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2672,7 +2675,7 @@
         <v>129.32761912511799</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2698,7 +2701,7 @@
         <v>129.33454593378599</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2724,7 +2727,7 @@
         <v>129.33141894784401</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2750,7 +2753,7 @@
         <v>129.33133707067299</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2776,7 +2779,7 @@
         <v>129.34715485530299</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2802,7 +2805,7 @@
         <v>129.33926986466699</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2828,7 +2831,7 @@
         <v>129.32761912511799</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2854,7 +2857,7 @@
         <v>129.309630937603</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2880,7 +2883,7 @@
         <v>129.31561270768299</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2906,7 +2909,7 @@
         <v>129.32761912511799</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2923,7 +2926,7 @@
         <v>82</v>
       </c>
       <c r="F71" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G71">
         <v>35.5609444477629</v>
@@ -2932,7 +2935,7 @@
         <v>129.331943041014</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2943,7 +2946,7 @@
         <v>191</v>
       </c>
       <c r="D72" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="E72" t="s">
         <v>10</v>
@@ -2958,7 +2961,7 @@
         <v>129.327504233165</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2966,16 +2969,16 @@
         <v>190</v>
       </c>
       <c r="C73" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D73" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="E73" t="s">
         <v>10</v>
       </c>
       <c r="F73" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G73">
         <v>35.555089355611798</v>
@@ -2984,7 +2987,7 @@
         <v>129.33393651216301</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2992,16 +2995,16 @@
         <v>190</v>
       </c>
       <c r="C74" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D74" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="E74" t="s">
         <v>10</v>
       </c>
       <c r="F74" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G74">
         <v>35.556408038012002</v>
@@ -3010,7 +3013,7 @@
         <v>129.32832432580301</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8">
       <c r="A75">
         <v>74</v>
       </c>
@@ -3018,10 +3021,10 @@
         <v>190</v>
       </c>
       <c r="C75" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D75" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E75" t="s">
         <v>93</v>
@@ -3036,24 +3039,24 @@
         <v>129.26523649600099</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C76" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D76" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E76" t="s">
         <v>10</v>
       </c>
       <c r="F76" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G76">
         <v>35.565261990764498</v>
@@ -3062,7 +3065,7 @@
         <v>129.32976548908499</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8">
       <c r="A77">
         <v>76</v>
       </c>
@@ -3070,19 +3073,19 @@
         <v>46160</v>
       </c>
       <c r="C77" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E77" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F77" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="F77" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:8">
       <c r="A78">
         <v>77</v>
       </c>
@@ -3090,19 +3093,19 @@
         <v>46160</v>
       </c>
       <c r="C78" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
       <c r="A79">
         <v>78</v>
       </c>
@@ -3110,19 +3113,19 @@
         <v>46164</v>
       </c>
       <c r="C79" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80">
         <v>79</v>
       </c>
@@ -3130,19 +3133,19 @@
         <v>46164</v>
       </c>
       <c r="C80" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D80" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="F80" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81">
         <v>80</v>
       </c>
@@ -3150,19 +3153,19 @@
         <v>46168</v>
       </c>
       <c r="C81" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E81" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F81" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82">
         <v>81</v>
       </c>
@@ -3170,16 +3173,16 @@
         <v>46168</v>
       </c>
       <c r="C82" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E82" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F82" s="4" t="s">
         <v>212</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/민원데이터.xlsx
+++ b/민원데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\민원관리 대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD72BE1-70F0-40A5-B80B-1897C97CE45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1D74D3-56C6-4878-9769-BEB0CD52CEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1365" windowWidth="22725" windowHeight="14835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1365" windowWidth="20550" windowHeight="14835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1092,7 +1092,7 @@
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.875" customWidth="1"/>
-    <col min="4" max="4" width="38.875" customWidth="1"/>
+    <col min="4" max="4" width="51.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3162,7 +3162,7 @@
         <v>209</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -3182,7 +3182,7 @@
         <v>209</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/민원데이터.xlsx
+++ b/민원데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\민원관리 대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1D74D3-56C6-4878-9769-BEB0CD52CEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5360D07-A9B8-477D-9903-A6C27A39EB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1365" windowWidth="20550" windowHeight="14835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="226">
   <si>
     <t>민원번호</t>
   </si>
@@ -714,6 +714,18 @@
   </si>
   <si>
     <t>번영로 368, 370 사이 전봇대에서 쓰레기 불법투기 잦아 CCTV 설치 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 성안동 1594-7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성안동 1594-7번지 공작물 설치(비닐하우스) 원상복구명령 통보 경위 확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김태욱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -771,7 +783,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -785,6 +797,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1087,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
@@ -3185,6 +3198,26 @@
         <v>202</v>
       </c>
     </row>
+    <row r="83" spans="1:6">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" s="5">
+        <v>46169</v>
+      </c>
+      <c r="C83" t="s">
+        <v>223</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F83" t="s">
+        <v>202</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/민원데이터.xlsx
+++ b/민원데이터.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\민원관리 대시보드\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\코딩\민원관리 대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5360D07-A9B8-477D-9903-A6C27A39EB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59121ACC-DB12-44F5-A73D-DAF8F8322F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14280" yWindow="600" windowWidth="18285" windowHeight="15030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="237">
   <si>
     <t>민원번호</t>
   </si>
@@ -580,48 +580,6 @@
     <t>성안동 청구아파트 택시승강장 지정 폐지 건의</t>
   </si>
   <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>구역전시장, 번영로 공영주차장 일대 가로등(보안등) 소등 시간 변경 요청</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>울산 중구 복산동 40-9</t>
-  </si>
-  <si>
-    <t>우천시 번영로드림파크 아파트 출입구로 우수 유입 발생함</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>울산 중구 학산동 80-1</t>
-  </si>
-  <si>
-    <t>울산 중구 학성동 464-39</t>
-  </si>
-  <si>
-    <t>울산 중구 학성동 436-11</t>
-  </si>
-  <si>
-    <t>울산 중구 다운동 247-5</t>
-  </si>
-  <si>
-    <t>민원인 30년 이상 척과천 하천 점용 및 경작으로 '원상복구 명령 공시 송달(5.7.)'불구, 점유 타당성 주장함. 사실관계 및 근거법령 확인요청</t>
-  </si>
-  <si>
-    <t>2026-05-13</t>
-  </si>
-  <si>
-    <t>울산 중구 북부순환도로 638-15</t>
-  </si>
-  <si>
-    <t>복산동 새중앙교회 앞 환경미화작업 요청</t>
-  </si>
-  <si>
     <t>접수자</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -630,10 +588,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>성안동 923</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>완료</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -674,13 +628,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>진행중</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>복산동 손골2길5 동덕현대아파트 104동 파손 탄력봉에 걸려 넘어지는 사례 발생하여 제거 요청</t>
-  </si>
-  <si>
     <t>울산 중구 복산동 319</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -705,27 +652,139 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>학성동 구역전족발 앞 횡단보도 맨홀뚜껑 유격 발생 및 주변 아스콘 파손 정비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>창현하우징 앞 맨홀뚜껑 유격 정비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>번영로 368, 370 사이 전봇대에서 쓰레기 불법투기 잦아 CCTV 설치 요청</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>울산 중구 성안동 1594-7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>김태욱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 성안동 923</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>의회 누리집</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>박경흠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>홍영진</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>강혜순</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>구역전시장, 번영로 공영주차장 일대 가로등(보안등) 소등 시간 변경 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>번영로드림파크 아파트 빗물 유입 및 침수 피해 개선 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>유곡동 480-12 일원 공공공지 주차장 장기주차로 인한 상가 이용자 주차공간 부족 문제</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>번영로 368, 370 사이 전봇대에서 쓰레기 불법투기 잦아 CCTV 설치 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>민원인 30년 이상 척과천(다운동 247-5) 하천 점용 및 경작으로 '원상복구 명령 공시 송달(5.7.)'불구, 점유 타당성 주장함. 사실관계 및 근거법령 확인요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>복산동 새중앙교회(북부순환도로 638-15) 앞 환경미화작업 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>복산동 손골2길5 동덕현대아파트 104동 파손 탄력봉에 걸려 넘어지는 사례 발생하여 제거 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>성안동 1594-7번지 공작물 설치(비닐하우스) 원상복구명령 통보 경위 확인</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>반구동 우남빌라(내황1길 25-3) 인근 오수관 준설 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>복산동 센트리지3단지 일원 방역</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>성안동 황암길(성안동 청구타운, 벽산e빌리지 ~ 야구장) 제초작업 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>조치불가</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>예정</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>학성동 구역전족발 앞 횡단보도 맨홀뚜껑 유격 발생 및 주변 아스콘 파손으로 주민 불안 가중</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>김태욱</t>
+    <t>울산 중구 유곡동 480-12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 복산동 40-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 학산동 189-12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 학산동 80-11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>창현하우징 앞 횡단보도 맨홀뚜껑 유격 발생 및 주변 아스콘 파손으로 주민 불안 가중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 학성동 464-39</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 학성동 436-11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 다운동 247-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 복산동 368-85</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산광역시 중구 학성동 156-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 592-23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 복산동 829</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 성안동 1669</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -783,21 +842,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1100,12 +1166,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.875" customWidth="1"/>
-    <col min="4" max="4" width="51.125" customWidth="1"/>
+    <col min="4" max="4" width="200.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1122,7 +1188,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -1434,7 +1500,7 @@
         <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="F13" t="s">
         <v>11</v>
@@ -2208,7 +2274,7 @@
         <v>121</v>
       </c>
       <c r="C43" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D43" t="s">
         <v>122</v>
@@ -2289,7 +2355,7 @@
         <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="G46">
         <v>35.557219330149202</v>
@@ -2419,7 +2485,7 @@
         <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="G51">
         <v>35.562228786253897</v>
@@ -2523,7 +2589,7 @@
         <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="G55">
         <v>35.558800966055898</v>
@@ -2621,12 +2687,12 @@
         <v>161</v>
       </c>
       <c r="D59" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F59" s="7" t="s">
         <v>60</v>
       </c>
       <c r="G59">
@@ -2652,7 +2718,7 @@
       <c r="E60" t="s">
         <v>10</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F60" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G60">
@@ -2678,7 +2744,7 @@
       <c r="E61" t="s">
         <v>10</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G61">
@@ -2704,7 +2770,7 @@
       <c r="E62" t="s">
         <v>10</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F62" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G62">
@@ -2730,7 +2796,7 @@
       <c r="E63" t="s">
         <v>10</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F63" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G63">
@@ -2756,7 +2822,7 @@
       <c r="E64" t="s">
         <v>36</v>
       </c>
-      <c r="F64" t="s">
+      <c r="F64" s="7" t="s">
         <v>60</v>
       </c>
       <c r="G64">
@@ -2782,7 +2848,7 @@
       <c r="E65" t="s">
         <v>36</v>
       </c>
-      <c r="F65" t="s">
+      <c r="F65" s="7" t="s">
         <v>60</v>
       </c>
       <c r="G65">
@@ -2808,7 +2874,7 @@
       <c r="E66" t="s">
         <v>10</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F66" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G66">
@@ -2834,7 +2900,7 @@
       <c r="E67" t="s">
         <v>10</v>
       </c>
-      <c r="F67" t="s">
+      <c r="F67" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G67">
@@ -2860,7 +2926,7 @@
       <c r="E68" t="s">
         <v>10</v>
       </c>
-      <c r="F68" t="s">
+      <c r="F68" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G68">
@@ -2886,7 +2952,7 @@
       <c r="E69" t="s">
         <v>82</v>
       </c>
-      <c r="F69" t="s">
+      <c r="F69" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G69">
@@ -2900,323 +2966,407 @@
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" t="s">
-        <v>185</v>
-      </c>
-      <c r="C70" t="s">
-        <v>165</v>
-      </c>
-      <c r="D70" t="s">
-        <v>186</v>
-      </c>
-      <c r="E70" t="s">
-        <v>10</v>
-      </c>
-      <c r="F70" t="s">
-        <v>11</v>
-      </c>
-      <c r="G70">
-        <v>35.558083481622702</v>
-      </c>
-      <c r="H70">
-        <v>129.32761912511799</v>
-      </c>
+      <c r="B70" s="2">
+        <v>46146</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" t="s">
-        <v>187</v>
-      </c>
-      <c r="C71" t="s">
-        <v>188</v>
-      </c>
-      <c r="D71" t="s">
-        <v>189</v>
-      </c>
-      <c r="E71" t="s">
-        <v>82</v>
-      </c>
-      <c r="F71" t="s">
-        <v>202</v>
-      </c>
-      <c r="G71">
-        <v>35.5609444477629</v>
-      </c>
-      <c r="H71">
-        <v>129.331943041014</v>
-      </c>
+      <c r="B71" s="2">
+        <v>46149</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
     </row>
     <row r="72" spans="1:8">
       <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" t="s">
-        <v>190</v>
-      </c>
-      <c r="C72" t="s">
-        <v>191</v>
-      </c>
-      <c r="D72" t="s">
-        <v>222</v>
-      </c>
-      <c r="E72" t="s">
-        <v>10</v>
-      </c>
-      <c r="F72" t="s">
-        <v>26</v>
-      </c>
-      <c r="G72">
-        <v>35.557736811282403</v>
-      </c>
-      <c r="H72">
-        <v>129.327504233165</v>
-      </c>
+      <c r="B72" s="2">
+        <v>46153</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
     </row>
     <row r="73" spans="1:8">
       <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73" t="s">
-        <v>190</v>
-      </c>
-      <c r="C73" t="s">
-        <v>192</v>
-      </c>
-      <c r="D73" t="s">
-        <v>221</v>
-      </c>
-      <c r="E73" t="s">
-        <v>10</v>
-      </c>
-      <c r="F73" t="s">
-        <v>202</v>
-      </c>
-      <c r="G73">
-        <v>35.555089355611798</v>
-      </c>
-      <c r="H73">
-        <v>129.33393651216301</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
+      <c r="B73" s="2">
+        <v>46153</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+    </row>
+    <row r="74" spans="1:8" ht="33">
       <c r="A74">
         <v>73</v>
       </c>
-      <c r="B74" t="s">
-        <v>190</v>
-      </c>
-      <c r="C74" t="s">
-        <v>193</v>
-      </c>
-      <c r="D74" t="s">
-        <v>220</v>
-      </c>
-      <c r="E74" t="s">
-        <v>10</v>
-      </c>
-      <c r="F74" t="s">
-        <v>202</v>
-      </c>
-      <c r="G74">
-        <v>35.556408038012002</v>
-      </c>
-      <c r="H74">
-        <v>129.32832432580301</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
+      <c r="B74" s="2">
+        <v>46153</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+    </row>
+    <row r="75" spans="1:8" ht="49.5">
       <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75" t="s">
-        <v>190</v>
-      </c>
-      <c r="C75" t="s">
-        <v>194</v>
-      </c>
-      <c r="D75" t="s">
-        <v>195</v>
-      </c>
-      <c r="E75" t="s">
-        <v>93</v>
-      </c>
-      <c r="F75" t="s">
-        <v>11</v>
-      </c>
-      <c r="G75">
-        <v>35.578724191624801</v>
-      </c>
-      <c r="H75">
-        <v>129.26523649600099</v>
-      </c>
+      <c r="B75" s="2">
+        <v>46153</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="2">
+        <v>46155</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F76" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="C76" t="s">
-        <v>197</v>
-      </c>
-      <c r="D76" t="s">
-        <v>198</v>
-      </c>
-      <c r="E76" t="s">
-        <v>10</v>
-      </c>
-      <c r="F76" t="s">
-        <v>202</v>
-      </c>
-      <c r="G76">
-        <v>35.565261990764498</v>
-      </c>
-      <c r="H76">
-        <v>129.32976548908499</v>
-      </c>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
     </row>
     <row r="77" spans="1:8">
       <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" s="1">
+      <c r="B77" s="2">
         <v>46160</v>
       </c>
-      <c r="C77" t="s">
-        <v>217</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>212</v>
-      </c>
+      <c r="C77" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
     </row>
     <row r="78" spans="1:8">
       <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B78" s="2">
         <v>46160</v>
       </c>
-      <c r="C78" t="s">
-        <v>217</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>211</v>
-      </c>
+      <c r="C78" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
     </row>
     <row r="79" spans="1:8">
       <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" s="1">
-        <v>46164</v>
-      </c>
-      <c r="C79" t="s">
-        <v>219</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>211</v>
-      </c>
+      <c r="B79" s="2">
+        <v>46161</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
     </row>
     <row r="80" spans="1:8">
       <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B80" s="2">
         <v>46164</v>
       </c>
-      <c r="C80" t="s">
-        <v>216</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
+      <c r="C80" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+    </row>
+    <row r="81" spans="1:8">
       <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81" s="1">
-        <v>46168</v>
-      </c>
-      <c r="C81" t="s">
-        <v>215</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
+      <c r="B81" s="2">
+        <v>46164</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82">
         <v>81</v>
       </c>
-      <c r="B82" s="1">
+      <c r="B82" s="2">
         <v>46168</v>
       </c>
-      <c r="C82" t="s">
-        <v>214</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="C82" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+    </row>
+    <row r="83" spans="1:8">
       <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83" s="5">
+      <c r="B83" s="2">
+        <v>46168</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2">
         <v>46169</v>
       </c>
-      <c r="C83" t="s">
-        <v>223</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F83" t="s">
-        <v>202</v>
-      </c>
+      <c r="C84" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2">
+        <v>46170</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2">
+        <v>46171</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2">
+        <v>46171</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/민원데이터.xlsx
+++ b/민원데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\코딩\민원관리 대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59121ACC-DB12-44F5-A73D-DAF8F8322F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93A6E1B-D65C-4F59-BBC9-3FF08A3A4248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14280" yWindow="600" windowWidth="18285" windowHeight="15030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28470" windowHeight="15030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -728,10 +728,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>예정</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>학성동 구역전족발 앞 횡단보도 맨홀뚜껑 유격 발생 및 주변 아스콘 파손으로 주민 불안 가중</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -786,13 +782,17 @@
   <si>
     <t>울산 중구 성안동 1669</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행중</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -842,28 +842,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1166,15 +1164,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H88"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:H87"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.875" customWidth="1"/>
     <col min="4" max="4" width="200.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1200,7 +1198,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1226,7 +1224,7 @@
         <v>129.334708123821</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1252,7 +1250,7 @@
         <v>129.34914011636599</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1278,7 +1276,7 @@
         <v>129.341655674116</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1304,7 +1302,7 @@
         <v>129.348784402462</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1330,7 +1328,7 @@
         <v>129.328386461436</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1356,7 +1354,7 @@
         <v>129.293406307109</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1382,7 +1380,7 @@
         <v>129.321138541696</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1408,7 +1406,7 @@
         <v>129.336443953188</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1434,7 +1432,7 @@
         <v>129.35126645610401</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1460,7 +1458,7 @@
         <v>129.34604022411801</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1486,7 +1484,7 @@
         <v>129.34512228457299</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1512,7 +1510,7 @@
         <v>129.265769674285</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1538,7 +1536,7 @@
         <v>129.328832230009</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1564,7 +1562,7 @@
         <v>129.32766567982</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1590,7 +1588,7 @@
         <v>129.32605295352801</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1616,7 +1614,7 @@
         <v>129.32736074607899</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1642,7 +1640,7 @@
         <v>129.327571456708</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1668,7 +1666,7 @@
         <v>129.26688519197299</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1694,7 +1692,7 @@
         <v>129.29811305216501</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1720,7 +1718,7 @@
         <v>129.29811305216501</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1746,7 +1744,7 @@
         <v>129.300962239363</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1772,7 +1770,7 @@
         <v>129.30058825465301</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1798,7 +1796,7 @@
         <v>129.30058825465301</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1824,7 +1822,7 @@
         <v>129.32200364813099</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1850,7 +1848,7 @@
         <v>129.32531570361701</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1876,7 +1874,7 @@
         <v>129.31827211577701</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1902,7 +1900,7 @@
         <v>129.3211136704</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1928,7 +1926,7 @@
         <v>129.28046149747701</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1954,7 +1952,7 @@
         <v>129.34220700976999</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1980,7 +1978,7 @@
         <v>129.308375901956</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2006,7 +2004,7 @@
         <v>129.279177893774</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2032,7 +2030,7 @@
         <v>129.31901602761101</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2058,7 +2056,7 @@
         <v>129.346181351555</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2084,7 +2082,7 @@
         <v>129.32388107690801</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2110,7 +2108,7 @@
         <v>129.33754632059299</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2136,7 +2134,7 @@
         <v>129.33754632059299</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2162,7 +2160,7 @@
         <v>129.32938991855301</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2188,7 +2186,7 @@
         <v>129.30858345615701</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2214,7 +2212,7 @@
         <v>129.32189922619699</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2240,7 +2238,7 @@
         <v>129.32189922619699</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2266,7 +2264,7 @@
         <v>129.31846356317999</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2286,7 +2284,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2312,7 +2310,7 @@
         <v>129.31021759453901</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2338,7 +2336,7 @@
         <v>129.30858345615701</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2364,7 +2362,7 @@
         <v>129.334901038727</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2390,7 +2388,7 @@
         <v>129.32268218764199</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2416,7 +2414,7 @@
         <v>129.32704582909801</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2442,7 +2440,7 @@
         <v>129.32991157348201</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2468,7 +2466,7 @@
         <v>129.30194271522601</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2494,7 +2492,7 @@
         <v>129.31749376133601</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2520,7 +2518,7 @@
         <v>129.31749376133601</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2546,7 +2544,7 @@
         <v>129.337495790666</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2572,7 +2570,7 @@
         <v>129.32938991855301</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2598,7 +2596,7 @@
         <v>129.33276957269501</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2624,7 +2622,7 @@
         <v>129.34719219842799</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2650,7 +2648,7 @@
         <v>129.337436690766</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2676,7 +2674,7 @@
         <v>129.30959998798701</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2692,7 +2690,7 @@
       <c r="E59" t="s">
         <v>15</v>
       </c>
-      <c r="F59" s="7" t="s">
+      <c r="F59" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G59">
@@ -2702,7 +2700,7 @@
         <v>129.34773887451399</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2718,7 +2716,7 @@
       <c r="E60" t="s">
         <v>10</v>
       </c>
-      <c r="F60" s="7" t="s">
+      <c r="F60" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G60">
@@ -2728,7 +2726,7 @@
         <v>129.32796607151101</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2744,7 +2742,7 @@
       <c r="E61" t="s">
         <v>10</v>
       </c>
-      <c r="F61" s="7" t="s">
+      <c r="F61" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G61">
@@ -2754,7 +2752,7 @@
         <v>129.32761912511799</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2770,7 +2768,7 @@
       <c r="E62" t="s">
         <v>10</v>
       </c>
-      <c r="F62" s="7" t="s">
+      <c r="F62" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G62">
@@ -2780,7 +2778,7 @@
         <v>129.33454593378599</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2796,7 +2794,7 @@
       <c r="E63" t="s">
         <v>10</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="F63" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G63">
@@ -2806,7 +2804,7 @@
         <v>129.33141894784401</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2822,7 +2820,7 @@
       <c r="E64" t="s">
         <v>36</v>
       </c>
-      <c r="F64" s="7" t="s">
+      <c r="F64" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G64">
@@ -2832,7 +2830,7 @@
         <v>129.33133707067299</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2848,7 +2846,7 @@
       <c r="E65" t="s">
         <v>36</v>
       </c>
-      <c r="F65" s="7" t="s">
+      <c r="F65" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G65">
@@ -2858,7 +2856,7 @@
         <v>129.34715485530299</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2874,7 +2872,7 @@
       <c r="E66" t="s">
         <v>10</v>
       </c>
-      <c r="F66" s="7" t="s">
+      <c r="F66" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G66">
@@ -2884,7 +2882,7 @@
         <v>129.33926986466699</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2900,7 +2898,7 @@
       <c r="E67" t="s">
         <v>10</v>
       </c>
-      <c r="F67" s="7" t="s">
+      <c r="F67" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G67">
@@ -2910,7 +2908,7 @@
         <v>129.32761912511799</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2926,7 +2924,7 @@
       <c r="E68" t="s">
         <v>10</v>
       </c>
-      <c r="F68" s="7" t="s">
+      <c r="F68" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G68">
@@ -2936,7 +2934,7 @@
         <v>129.309630937603</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2952,7 +2950,7 @@
       <c r="E69" t="s">
         <v>82</v>
       </c>
-      <c r="F69" s="7" t="s">
+      <c r="F69" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G69">
@@ -2962,411 +2960,365 @@
         <v>129.31561270768299</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70" s="1">
         <v>46146</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D70" s="5" t="s">
+      <c r="C70" t="s">
+        <v>225</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="E70" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F70" s="5" t="s">
+      <c r="F70" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-    </row>
-    <row r="71" spans="1:8">
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B71" s="1">
         <v>46149</v>
       </c>
-      <c r="C71" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="D71" s="3" t="s">
+      <c r="C71" t="s">
+        <v>224</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E71" s="4" t="s">
+      <c r="E71" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="F71" s="5" t="s">
+      <c r="F71" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-    </row>
-    <row r="72" spans="1:8">
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B72" s="1">
         <v>46153</v>
       </c>
-      <c r="C72" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="D72" s="5" t="s">
+      <c r="C72" t="s">
+        <v>226</v>
+      </c>
+      <c r="D72" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="E72" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F72" s="5" t="s">
+      <c r="F72" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-    </row>
-    <row r="73" spans="1:8">
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73" s="2">
+      <c r="B73" s="1">
         <v>46153</v>
       </c>
-      <c r="C73" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="D73" s="6" t="s">
+      <c r="C73" t="s">
         <v>228</v>
       </c>
-      <c r="E73" s="4" t="s">
+      <c r="D73" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="E73" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F73" s="5" t="s">
+      <c r="F73" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-    </row>
-    <row r="74" spans="1:8" ht="33">
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
-      <c r="B74" s="2">
+      <c r="B74" s="1">
         <v>46153</v>
       </c>
-      <c r="C74" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="E74" s="4" t="s">
+      <c r="C74" t="s">
+        <v>229</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E74" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F74" s="5" t="s">
+      <c r="F74" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-    </row>
-    <row r="75" spans="1:8" ht="49.5">
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75" s="1">
         <v>46153</v>
       </c>
-      <c r="C75" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="D75" s="6" t="s">
+      <c r="C75" t="s">
+        <v>230</v>
+      </c>
+      <c r="D75" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="E75" s="4" t="s">
+      <c r="E75" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="F75" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
-    </row>
-    <row r="76" spans="1:8">
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" s="2">
+      <c r="B76" s="1">
         <v>46155</v>
       </c>
-      <c r="C76" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="D76" s="5" t="s">
+      <c r="C76" t="s">
+        <v>231</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E76" s="4" t="s">
+      <c r="E76" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F76" s="5" t="s">
+      <c r="F76" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-    </row>
-    <row r="77" spans="1:8">
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" s="2">
+      <c r="B77" s="1">
         <v>46160</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C77" t="s">
         <v>200</v>
       </c>
-      <c r="D77" s="5" t="s">
+      <c r="D77" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="E77" s="4" t="s">
+      <c r="E77" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F77" s="5" t="s">
+      <c r="F77" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-    </row>
-    <row r="78" spans="1:8">
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78" s="1">
         <v>46160</v>
       </c>
-      <c r="C78" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="D78" s="5" t="s">
+      <c r="C78" t="s">
+        <v>232</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E78" s="4" t="s">
+      <c r="E78" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F78" s="5" t="s">
+      <c r="F78" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-    </row>
-    <row r="79" spans="1:8">
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" s="2">
+      <c r="B79" s="1">
         <v>46161</v>
       </c>
-      <c r="C79" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="D79" s="5" t="s">
+      <c r="C79" t="s">
+        <v>223</v>
+      </c>
+      <c r="D79" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="E79" s="4" t="s">
+      <c r="E79" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="F79" s="5" t="s">
+      <c r="F79" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-    </row>
-    <row r="80" spans="1:8">
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" s="2">
+      <c r="B80" s="1">
         <v>46164</v>
       </c>
-      <c r="C80" s="8" t="s">
+      <c r="C80" t="s">
         <v>202</v>
       </c>
-      <c r="D80" s="5" t="s">
+      <c r="D80" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="E80" s="4" t="s">
+      <c r="E80" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F80" s="5" t="s">
+      <c r="F80" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-    </row>
-    <row r="81" spans="1:8">
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81" s="2">
+      <c r="B81" s="1">
         <v>46164</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="C81" t="s">
         <v>199</v>
       </c>
-      <c r="D81" s="5" t="s">
+      <c r="D81" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="E81" s="4" t="s">
+      <c r="E81" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F81" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-    </row>
-    <row r="82" spans="1:8">
+      <c r="F81" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
-      <c r="B82" s="2">
+      <c r="B82" s="1">
         <v>46168</v>
       </c>
-      <c r="C82" s="8" t="s">
+      <c r="C82" t="s">
         <v>198</v>
       </c>
-      <c r="D82" s="5" t="s">
+      <c r="D82" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E82" s="4" t="s">
+      <c r="E82" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F82" s="5" t="s">
+      <c r="F82" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-    </row>
-    <row r="83" spans="1:8">
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83" s="1">
         <v>46168</v>
       </c>
-      <c r="C83" s="8" t="s">
+      <c r="C83" t="s">
         <v>197</v>
       </c>
-      <c r="D83" s="5" t="s">
+      <c r="D83" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="E83" s="4" t="s">
+      <c r="E83" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F83" s="5" t="s">
+      <c r="F83" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
-    </row>
-    <row r="84" spans="1:8">
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84" s="1">
         <v>46169</v>
       </c>
-      <c r="C84" s="8" t="s">
+      <c r="C84" t="s">
         <v>203</v>
       </c>
-      <c r="D84" s="5" t="s">
+      <c r="D84" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="E84" s="4" t="s">
+      <c r="E84" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F84" s="5" t="s">
+      <c r="F84" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
-    </row>
-    <row r="85" spans="1:8">
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
-      <c r="B85" s="2">
+      <c r="B85" s="1">
         <v>46170</v>
       </c>
-      <c r="C85" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="D85" s="5" t="s">
+      <c r="C85" t="s">
+        <v>233</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="E85" s="4" t="s">
+      <c r="E85" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="F85" s="5" t="s">
+      <c r="F85" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="G85" s="1"/>
-      <c r="H85" s="1"/>
-    </row>
-    <row r="86" spans="1:8">
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
-      <c r="B86" s="2">
+      <c r="B86" s="1">
         <v>46171</v>
       </c>
-      <c r="C86" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="D86" s="5" t="s">
+      <c r="C86" t="s">
+        <v>234</v>
+      </c>
+      <c r="D86" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="E86" s="4" t="s">
+      <c r="E86" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F86" s="5" t="s">
+      <c r="F86" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
-    </row>
-    <row r="87" spans="1:8">
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
-      <c r="B87" s="2">
+      <c r="B87" s="1">
         <v>46171</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="C87" t="s">
+        <v>235</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F87" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="D87" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
-    </row>
-    <row r="88" spans="1:8">
-      <c r="A88" s="1"/>
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
